--- a/data/trans_orig/IP07_A11_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07_A11_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el adulto en 2023 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el/la adulto/a en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2564</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4106</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>608</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>657</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3041</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1172,74 +1172,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28679</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25649</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30343</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>26437</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22941</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27805</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>22812</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>20159</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>24081</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>94,73%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>83,71%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>33896</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>30595</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35717</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>83,99%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>78</t>
@@ -1247,27 +1247,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>60333</t>
+          <t>51491</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56151</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62770</t>
+          <t>53793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>30968</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>30968</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>30968</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>27805</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>27805</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>27805</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>64232</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>64232</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64232</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3549</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11400</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>10129</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>15,76%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3549</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>11135</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4109</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1096</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4444</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4423</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4864</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7716</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>358</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12451</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3829</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9414</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>57283</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>49472</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>62304</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>70435</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>63470</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>75749</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>90,61%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61178</t>
+          <t>44655</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52605</t>
+          <t>39458</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66940</t>
+          <t>48779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>131614</t>
+          <t>101938</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>120734</t>
+          <t>93151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141396</t>
+          <t>108586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>67851</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>67851</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>67851</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77736</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77736</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77736</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>150055</t>
+          <t>119993</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>150055</t>
+          <t>119993</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>150055</t>
+          <t>119993</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -2197,107 +2197,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3241</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3387</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3316</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -2310,107 +2310,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>341</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1763</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2389</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>2286</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2197</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5697</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2861</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9845</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1254</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3932</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1242</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3799</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>6224</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>3051</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10837</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>23072</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>30645</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>77,19%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>66,03%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>87,7%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>28134</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>24819</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>30011</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>80,94%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>28109</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33493</t>
+          <t>29974</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>57968</t>
+          <t>55082</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51988</t>
+          <t>50055</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62325</t>
+          <t>59240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>34942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>34942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>34942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>30663</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>30663</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>30663</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38623</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38623</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38623</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>69285</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>69285</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69285</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>3177</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7472</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>19,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -2879,107 +2879,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5820</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5447</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>4937</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>5044</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2504</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>8164</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>16,47%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5483</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>7117</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>8280</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>983</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8763</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,68%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6839</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1539</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7374</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>17,46%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2080</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7965</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>370</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>43104</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>35402</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>47645</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>86,95%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>71,41%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>32649</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>27067</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>36198</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>83,34%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>69,09%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>92,4%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>45977</t>
+          <t>34248</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37762</t>
+          <t>28196</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50676</t>
+          <t>38316</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>78626</t>
+          <t>77352</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>69456</t>
+          <t>68024</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>84423</t>
+          <t>83611</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>49575</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>49575</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>49575</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>39177</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>39177</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>39177</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>41189</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>41189</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>41189</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>90764</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>90764</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>90764</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,107 +3448,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20,57%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1919</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5243</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3508</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2541</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1136</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>4083</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>33,25%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>3642</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>1646</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>6565</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>537</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>3058</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>6382</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>24,97%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>5608</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>29,73%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>13166</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>21113</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>68,2%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>51,51%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>82,6%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>14560</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>11309</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>16711</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>77,21%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>59,97%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>88,61%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26501</t>
+          <t>26352</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>36145</t>
+          <t>37160</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>18859</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>18859</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>18859</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,107 +4130,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>12,84%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>2749</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -4243,107 +4243,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>2480</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>572</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -4582,74 +4582,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>23008</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>20094</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>24062</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>95,62%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>83,51%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>22955</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>20234</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>84,16%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>24048</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>21117</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>25192</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>83,82%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>25237</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>22667</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>25998</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>87,19%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>74</t>
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>48193</t>
+          <t>47055</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>44227</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>49503</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>24062</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>24062</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>24062</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>49253</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>49253</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>49253</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>5816</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>3804</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>1439</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>7946</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>5596</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>5199</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>5071</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>494</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11566</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>5786</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>24578</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>28,19%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>5653</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>2516</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>10942</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>34814</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>21845</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>31385</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>8580</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>4408</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>15912</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>18,25%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>4025</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>8271</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>11,44%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>15731</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>20282</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>64302</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>52588</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>71798</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>73,74%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>60,31%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>82,34%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>57459</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>50416</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>62959</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>79,47%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>87,08%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>67893</t>
+          <t>58072</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>52600</t>
+          <t>50789</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>78072</t>
+          <t>64167</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>125352</t>
+          <t>122374</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>108645</t>
+          <t>108443</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>136095</t>
+          <t>132069</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>87200</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>87200</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>87200</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>72301</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>72301</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>72301</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>167898</t>
+          <t>161139</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>167898</t>
+          <t>161139</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>167898</t>
+          <t>161139</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>3932</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>9310</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>6149</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>2262</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>7542</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>3660</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>8310</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -5607,107 +5607,107 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>5790</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>1693</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>6146</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>1693</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>5953</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>4871</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -5720,107 +5720,107 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>950</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>4766</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>5155</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>6181</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>4187</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -5833,72 +5833,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>17457</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>25855</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>17,49%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>25,9%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>9012</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>4367</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>14666</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>25111</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>34164</t>
+          <t>39058</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -5946,72 +5946,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>77486</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>68787</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>85034</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>77,62%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>68,91%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>85,18%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>66150</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>58923</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>71412</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>84,19%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>90,89%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>72478</t>
+          <t>74495</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>64994</t>
+          <t>67106</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>79826</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>138628</t>
+          <t>151981</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>128743</t>
+          <t>140030</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>146902</t>
+          <t>161771</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>99825</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>99825</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>99825</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>78569</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>78569</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>78569</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>93106</t>
+          <t>88303</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>93106</t>
+          <t>88303</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>93106</t>
+          <t>88303</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>171675</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>171675</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>171675</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>15497</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>9591</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>25579</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>11289</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>18260</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>39966</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>9035</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>5549</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>10229</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>17478</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>17694</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>9440</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>31362</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>10806</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>6363</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>17662</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>47243</t>
+          <t>19440</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>57408</t>
+          <t>45246</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>44337</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>33724</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>58156</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>22728</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>15577</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>32350</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>58709</t>
+          <t>33975</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>66873</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>52815</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>81402</t>
+          <t>82889</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>338269</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>320413</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>352690</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>80,54%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>76,29%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>83,98%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>318780</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>306785</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>332663</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>86,35%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>353931</t>
+          <t>301828</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>332203</t>
+          <t>288634</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>370907</t>
+          <t>313203</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>672711</t>
+          <t>640096</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>647219</t>
+          <t>619358</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>695108</t>
+          <t>660123</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
